--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33523F8-2521-4655-97DC-46080B356F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86A61F4-2B8A-4E50-8CD9-071554678F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -4177,7 +4177,7 @@
       <c r="B151" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="2" t="s">
         <v>427</v>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       <c r="A152" t="s">
         <v>4</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="5" t="s">
         <v>357</v>
       </c>
       <c r="C152" s="2" t="s">
@@ -4519,8 +4519,9 @@
     <hyperlink ref="C169" r:id="rId136" xr:uid="{62F348E3-0B8D-47B6-8951-1599E9F9BD60}"/>
     <hyperlink ref="C149" r:id="rId137" xr:uid="{0E01F3DE-80E8-4F2E-B432-B3737CFA4D99}"/>
     <hyperlink ref="C150" r:id="rId138" xr:uid="{FA524709-47E9-490F-A089-312860B0DC84}"/>
+    <hyperlink ref="C151" r:id="rId139" xr:uid="{2478E041-032D-4CDD-A361-592BCEF9A589}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId139"/>
+  <pageSetup orientation="portrait" r:id="rId140"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86A61F4-2B8A-4E50-8CD9-071554678F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF122FF-2BF3-4B16-9FF3-6FF31EC7769B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -4194,13 +4194,13 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>8</v>
-      </c>
-      <c r="B153" t="s">
-        <v>352</v>
+        <v>4</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
@@ -4216,13 +4216,13 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
@@ -4504,7 +4504,7 @@
     <hyperlink ref="C145" r:id="rId121" xr:uid="{AA4F5772-E99C-4FA5-8C55-0181B3B31431}"/>
     <hyperlink ref="C147" r:id="rId122" xr:uid="{BB6B1DBE-0790-4C67-B2CD-03C5DF13EE91}"/>
     <hyperlink ref="C152" r:id="rId123" xr:uid="{D7949A5B-0952-40E7-B0C6-1772D9DCD774}"/>
-    <hyperlink ref="C155" r:id="rId124" xr:uid="{2D3D6F71-FC76-4746-93A9-E61CEF274DF2}"/>
+    <hyperlink ref="C153" r:id="rId124" xr:uid="{2D3D6F71-FC76-4746-93A9-E61CEF274DF2}"/>
     <hyperlink ref="C137" r:id="rId125" xr:uid="{E17CCA86-EE67-40CC-8E48-F995E9124648}"/>
     <hyperlink ref="C138" r:id="rId126" xr:uid="{E62A1C12-A8AE-482B-86EA-0CEFC510063E}"/>
     <hyperlink ref="C141" r:id="rId127" xr:uid="{135DD339-026F-4D89-8A58-A0DAC0070079}"/>
@@ -4515,7 +4515,7 @@
     <hyperlink ref="C143" r:id="rId132" xr:uid="{146F583A-8654-483C-A3FE-787D22E6F0BF}"/>
     <hyperlink ref="C146" r:id="rId133" xr:uid="{7657DEC4-1594-43D6-B1E6-AF7A3F185B0D}"/>
     <hyperlink ref="C148" r:id="rId134" xr:uid="{7ECE2E4A-0794-46F4-ACC9-C940E483649D}"/>
-    <hyperlink ref="C153" r:id="rId135" xr:uid="{E7E53EF3-B599-4F18-B473-A861B6EC834C}"/>
+    <hyperlink ref="C155" r:id="rId135" xr:uid="{E7E53EF3-B599-4F18-B473-A861B6EC834C}"/>
     <hyperlink ref="C169" r:id="rId136" xr:uid="{62F348E3-0B8D-47B6-8951-1599E9F9BD60}"/>
     <hyperlink ref="C149" r:id="rId137" xr:uid="{0E01F3DE-80E8-4F2E-B432-B3737CFA4D99}"/>
     <hyperlink ref="C150" r:id="rId138" xr:uid="{FA524709-47E9-490F-A089-312860B0DC84}"/>

--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF122FF-2BF3-4B16-9FF3-6FF31EC7769B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E76239C-D974-486B-B9CD-45B6C373F46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -3759,7 +3759,7 @@
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B113" t="s">
+      <c r="B113" s="3" t="s">
         <v>425</v>
       </c>
     </row>

--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E76239C-D974-486B-B9CD-45B6C373F46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBD4115-99D4-45FD-B761-49296CB5E271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="426">
   <si>
     <t>Difficulty</t>
   </si>
@@ -965,12 +965,6 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/merge-k-sorted-lists</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Link</t>
   </si>
   <si>
     <t xml:space="preserve"> Maximum Coins From K Consecutive Bags</t>
@@ -3760,7 +3754,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B113" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
@@ -3768,10 +3762,10 @@
         <v>0</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>315</v>
+        <v>1</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>316</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
@@ -3779,10 +3773,10 @@
         <v>8</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C115" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
@@ -3790,10 +3784,10 @@
         <v>8</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C116" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
@@ -3801,10 +3795,10 @@
         <v>8</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C117" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
@@ -3812,10 +3806,10 @@
         <v>12</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C118" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
@@ -3823,10 +3817,10 @@
         <v>12</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
@@ -3834,10 +3828,10 @@
         <v>8</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
@@ -3845,10 +3839,10 @@
         <v>8</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
@@ -3856,10 +3850,10 @@
         <v>8</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
@@ -3867,10 +3861,10 @@
         <v>4</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
@@ -3878,10 +3872,10 @@
         <v>8</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
@@ -3889,10 +3883,10 @@
         <v>8</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
@@ -3900,10 +3894,10 @@
         <v>8</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
@@ -3911,10 +3905,10 @@
         <v>8</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
@@ -3922,10 +3916,10 @@
         <v>4</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
@@ -3933,10 +3927,10 @@
         <v>8</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
@@ -3944,10 +3938,10 @@
         <v>8</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
@@ -3955,10 +3949,10 @@
         <v>8</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
@@ -3966,10 +3960,10 @@
         <v>8</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
@@ -3977,10 +3971,10 @@
         <v>8</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
@@ -3988,10 +3982,10 @@
         <v>8</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
@@ -3999,10 +3993,10 @@
         <v>4</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
@@ -4010,10 +4004,10 @@
         <v>8</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
@@ -4021,10 +4015,10 @@
         <v>8</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
@@ -4032,10 +4026,10 @@
         <v>8</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
@@ -4043,10 +4037,10 @@
         <v>4</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
@@ -4054,10 +4048,10 @@
         <v>4</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -4065,10 +4059,10 @@
         <v>4</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
@@ -4076,10 +4070,10 @@
         <v>12</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -4087,10 +4081,10 @@
         <v>12</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
@@ -4098,10 +4092,10 @@
         <v>8</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
@@ -4109,10 +4103,10 @@
         <v>4</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
@@ -4120,10 +4114,10 @@
         <v>12</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
@@ -4131,10 +4125,10 @@
         <v>4</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
@@ -4142,10 +4136,10 @@
         <v>4</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
@@ -4153,10 +4147,10 @@
         <v>8</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -4164,10 +4158,10 @@
         <v>8</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -4175,10 +4169,10 @@
         <v>8</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -4186,10 +4180,10 @@
         <v>4</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
@@ -4197,10 +4191,10 @@
         <v>4</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
@@ -4208,10 +4202,10 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C154" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
@@ -4219,10 +4213,10 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
@@ -4230,10 +4224,10 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
@@ -4241,10 +4235,10 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
@@ -4252,10 +4246,10 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C158" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
@@ -4263,10 +4257,10 @@
         <v>4</v>
       </c>
       <c r="B159" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C159" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
@@ -4274,10 +4268,10 @@
         <v>4</v>
       </c>
       <c r="B160" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C160" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
@@ -4285,10 +4279,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C161" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -4296,10 +4290,10 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
@@ -4307,10 +4301,10 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C163" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
@@ -4318,10 +4312,10 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C164" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -4329,10 +4323,10 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -4340,10 +4334,10 @@
         <v>4</v>
       </c>
       <c r="B166" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -4351,10 +4345,10 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C167" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
@@ -4362,10 +4356,10 @@
         <v>4</v>
       </c>
       <c r="B168" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
@@ -4373,10 +4367,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>

--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBD4115-99D4-45FD-B761-49296CB5E271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07600F97-46EB-47E4-9491-1AFC70BA7994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -2191,7 +2191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C267225-C50B-440B-AFF3-5C88037D1483}">
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
@@ -4201,10 +4201,10 @@
       <c r="A154" t="s">
         <v>8</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C154" s="2" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
       <c r="A155" t="s">
         <v>8</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="5" t="s">
         <v>350</v>
       </c>
       <c r="C155" s="2" t="s">
@@ -4223,7 +4223,7 @@
       <c r="A156" t="s">
         <v>8</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="1" t="s">
         <v>339</v>
       </c>
       <c r="C156" s="2" t="s">
@@ -4234,7 +4234,7 @@
       <c r="A157" t="s">
         <v>8</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="1" t="s">
         <v>340</v>
       </c>
       <c r="C157" s="2" t="s">
@@ -4245,43 +4245,32 @@
       <c r="A158" t="s">
         <v>8</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C158" s="2" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>4</v>
-      </c>
-      <c r="B159" t="s">
+        <v>12</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="2" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>4</v>
-      </c>
-      <c r="B160" t="s">
-        <v>362</v>
-      </c>
-      <c r="C160" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
         <v>12</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B160" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C160" s="2" t="s">
         <v>417</v>
       </c>
     </row>
@@ -4371,6 +4360,17 @@
       </c>
       <c r="C169" s="2" t="s">
         <v>407</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>12</v>
+      </c>
+      <c r="B170" t="s">
+        <v>362</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -4514,8 +4514,13 @@
     <hyperlink ref="C149" r:id="rId137" xr:uid="{0E01F3DE-80E8-4F2E-B432-B3737CFA4D99}"/>
     <hyperlink ref="C150" r:id="rId138" xr:uid="{FA524709-47E9-490F-A089-312860B0DC84}"/>
     <hyperlink ref="C151" r:id="rId139" xr:uid="{2478E041-032D-4CDD-A361-592BCEF9A589}"/>
+    <hyperlink ref="C154" r:id="rId140" xr:uid="{2C4DD23A-F9F2-479B-8C24-775407314589}"/>
+    <hyperlink ref="C158" r:id="rId141" xr:uid="{A75441B6-9439-4B62-8CA0-49107F5ED25F}"/>
+    <hyperlink ref="C159" r:id="rId142" xr:uid="{D1721C97-BCA6-44F5-AE02-814D7DCC88FB}"/>
+    <hyperlink ref="C170" r:id="rId143" xr:uid="{E0507AEA-A22E-45A8-AE1A-2EEE3DA0A0C9}"/>
+    <hyperlink ref="C160" r:id="rId144" xr:uid="{10462578-5E0B-41B2-8B9E-998C479B87AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId140"/>
+  <pageSetup orientation="portrait" r:id="rId145"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07600F97-46EB-47E4-9491-1AFC70BA7994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BF0520-6A0F-4B88-BE75-70DCA158B32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -2191,7 +2191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C267225-C50B-440B-AFF3-5C88037D1483}">
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
@@ -3686,10 +3686,10 @@
       <c r="A107" t="s">
         <v>8</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D107" t="s">
@@ -4274,11 +4274,22 @@
         <v>417</v>
       </c>
     </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>8</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="5" t="s">
         <v>329</v>
       </c>
       <c r="C162" s="2" t="s">
@@ -4287,89 +4298,78 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>8</v>
-      </c>
-      <c r="B163" t="s">
-        <v>366</v>
-      </c>
-      <c r="C163" t="s">
-        <v>420</v>
+        <v>4</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>8</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C164" s="2" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>8</v>
-      </c>
-      <c r="B165" t="s">
-        <v>333</v>
+        <v>12</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>4</v>
-      </c>
-      <c r="B166" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>8</v>
+      </c>
+      <c r="B173" t="s">
+        <v>333</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>12</v>
+      </c>
+      <c r="B174" t="s">
         <v>315</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C174" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
-        <v>8</v>
-      </c>
-      <c r="B167" t="s">
-        <v>341</v>
-      </c>
-      <c r="C167" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
-        <v>4</v>
-      </c>
-      <c r="B168" t="s">
-        <v>342</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
         <v>12</v>
       </c>
-      <c r="B169" t="s">
-        <v>353</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
-        <v>12</v>
-      </c>
-      <c r="B170" t="s">
+      <c r="B175" t="s">
         <v>362</v>
       </c>
-      <c r="C170" s="2" t="s">
+      <c r="C175" s="2" t="s">
         <v>416</v>
       </c>
     </row>
@@ -4484,8 +4484,8 @@
     <hyperlink ref="C162" r:id="rId107" xr:uid="{A1ED9BDA-ACA5-4B6A-8562-F21A1133879C}"/>
     <hyperlink ref="C129" r:id="rId108" xr:uid="{B6255BB1-281E-4413-AA60-7F650B88AE31}"/>
     <hyperlink ref="C130" r:id="rId109" xr:uid="{5C4B4859-6F57-41C9-A767-78BAA0185AC6}"/>
-    <hyperlink ref="C165" r:id="rId110" xr:uid="{50F977BC-A580-40CA-99A8-12622C6DC83B}"/>
-    <hyperlink ref="C166" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
+    <hyperlink ref="C173" r:id="rId110" xr:uid="{50F977BC-A580-40CA-99A8-12622C6DC83B}"/>
+    <hyperlink ref="C174" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
     <hyperlink ref="C131" r:id="rId112" xr:uid="{812567D3-953B-4D03-AE8C-43607B67208C}"/>
     <hyperlink ref="C132" r:id="rId113" xr:uid="{9F5366E7-2B07-4547-A415-A41154DAF6E8}"/>
     <hyperlink ref="C133" r:id="rId114" xr:uid="{EC814759-6574-4DB1-9594-36303369F2E3}"/>
@@ -4503,24 +4503,28 @@
     <hyperlink ref="C138" r:id="rId126" xr:uid="{E62A1C12-A8AE-482B-86EA-0CEFC510063E}"/>
     <hyperlink ref="C141" r:id="rId127" xr:uid="{135DD339-026F-4D89-8A58-A0DAC0070079}"/>
     <hyperlink ref="C144" r:id="rId128" xr:uid="{CA906D41-EBEE-4DBF-AF9C-825A4EACE5D9}"/>
-    <hyperlink ref="C168" r:id="rId129" xr:uid="{2A4866D6-0938-4980-B2F8-C2D12CDF93FE}"/>
+    <hyperlink ref="C163" r:id="rId129" xr:uid="{2A4866D6-0938-4980-B2F8-C2D12CDF93FE}"/>
     <hyperlink ref="C139" r:id="rId130" xr:uid="{944E35D1-9505-439F-B4D5-13DC55ECD476}"/>
     <hyperlink ref="C140" r:id="rId131" xr:uid="{5CA067C0-559D-49DD-9CBC-05FF25FDB146}"/>
     <hyperlink ref="C143" r:id="rId132" xr:uid="{146F583A-8654-483C-A3FE-787D22E6F0BF}"/>
     <hyperlink ref="C146" r:id="rId133" xr:uid="{7657DEC4-1594-43D6-B1E6-AF7A3F185B0D}"/>
     <hyperlink ref="C148" r:id="rId134" xr:uid="{7ECE2E4A-0794-46F4-ACC9-C940E483649D}"/>
     <hyperlink ref="C155" r:id="rId135" xr:uid="{E7E53EF3-B599-4F18-B473-A861B6EC834C}"/>
-    <hyperlink ref="C169" r:id="rId136" xr:uid="{62F348E3-0B8D-47B6-8951-1599E9F9BD60}"/>
+    <hyperlink ref="C165" r:id="rId136" xr:uid="{62F348E3-0B8D-47B6-8951-1599E9F9BD60}"/>
     <hyperlink ref="C149" r:id="rId137" xr:uid="{0E01F3DE-80E8-4F2E-B432-B3737CFA4D99}"/>
     <hyperlink ref="C150" r:id="rId138" xr:uid="{FA524709-47E9-490F-A089-312860B0DC84}"/>
     <hyperlink ref="C151" r:id="rId139" xr:uid="{2478E041-032D-4CDD-A361-592BCEF9A589}"/>
     <hyperlink ref="C154" r:id="rId140" xr:uid="{2C4DD23A-F9F2-479B-8C24-775407314589}"/>
     <hyperlink ref="C158" r:id="rId141" xr:uid="{A75441B6-9439-4B62-8CA0-49107F5ED25F}"/>
     <hyperlink ref="C159" r:id="rId142" xr:uid="{D1721C97-BCA6-44F5-AE02-814D7DCC88FB}"/>
-    <hyperlink ref="C170" r:id="rId143" xr:uid="{E0507AEA-A22E-45A8-AE1A-2EEE3DA0A0C9}"/>
+    <hyperlink ref="C175" r:id="rId143" xr:uid="{E0507AEA-A22E-45A8-AE1A-2EEE3DA0A0C9}"/>
     <hyperlink ref="C160" r:id="rId144" xr:uid="{10462578-5E0B-41B2-8B9E-998C479B87AC}"/>
+    <hyperlink ref="C164" r:id="rId145" xr:uid="{71170706-AE5E-4242-AB9A-7D79E1339A5E}"/>
+    <hyperlink ref="C161" r:id="rId146" xr:uid="{DCBD3C2C-5441-4A9F-92FD-4B9D3CCF6F46}"/>
+    <hyperlink ref="C166" r:id="rId147" xr:uid="{36022F00-DC73-4627-8041-3B429A0E69A8}"/>
+    <hyperlink ref="C107" r:id="rId148" xr:uid="{3A053D4A-EB59-41B8-92A9-6039717F7935}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId145"/>
+  <pageSetup orientation="portrait" r:id="rId149"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BF0520-6A0F-4B88-BE75-70DCA158B32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D15F0EA-5198-462D-94B3-AB06C83F2541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="426">
   <si>
     <t>Difficulty</t>
   </si>
@@ -1291,13 +1291,13 @@
     <t>https://leetcode.com/problems/longest-valid-parentheses/description/</t>
   </si>
   <si>
-    <t>(Set - 2)</t>
-  </si>
-  <si>
     <t>Most Profitable Path in a Tree</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/most-profitable-path-in-a-tree/description/</t>
+  </si>
+  <si>
+    <t>(PART-B)</t>
   </si>
 </sst>
 </file>
@@ -2191,7 +2191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C267225-C50B-440B-AFF3-5C88037D1483}">
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
@@ -3700,7 +3700,7 @@
       <c r="A108" t="s">
         <v>8</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C108" s="2" t="s">
@@ -3712,82 +3712,90 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>8</v>
-      </c>
-      <c r="B109" t="s">
-        <v>242</v>
+        <v>12</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="D109" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>52</v>
-      </c>
-      <c r="C110" t="s">
-        <v>53</v>
+        <v>242</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="D110" t="s">
-        <v>54</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>12</v>
-      </c>
-      <c r="B111" t="s">
-        <v>310</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D111" t="s">
-        <v>312</v>
+      <c r="B111" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>8</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C112" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B113" s="3" t="s">
-        <v>423</v>
+      <c r="A113" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C113" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>2</v>
+      <c r="A114" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C114" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C115" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C116" t="s">
-        <v>377</v>
+        <v>318</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
@@ -3795,43 +3803,43 @@
         <v>8</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C117" t="s">
-        <v>375</v>
+        <v>319</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C118" t="s">
-        <v>384</v>
+        <v>320</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
@@ -3839,10 +3847,10 @@
         <v>8</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
@@ -3850,21 +3858,21 @@
         <v>8</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
@@ -3872,21 +3880,21 @@
         <v>8</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
@@ -3894,10 +3902,10 @@
         <v>8</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
@@ -3905,32 +3913,32 @@
         <v>8</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>8</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>331</v>
+      <c r="B129" s="5" t="s">
+        <v>335</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
@@ -3938,10 +3946,10 @@
         <v>8</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
@@ -3949,21 +3957,21 @@
         <v>8</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>8</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>335</v>
+        <v>4</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
@@ -3971,10 +3979,10 @@
         <v>8</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
@@ -3982,98 +3990,98 @@
         <v>8</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -4081,21 +4089,21 @@
         <v>12</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
@@ -4103,65 +4111,65 @@
         <v>4</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>352</v>
+        <v>423</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>8</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>354</v>
+        <v>4</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>355</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -4169,32 +4177,32 @@
         <v>8</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>424</v>
+        <v>357</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
@@ -4202,43 +4210,43 @@
         <v>8</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>8</v>
       </c>
-      <c r="B155" s="5" t="s">
-        <v>350</v>
+      <c r="B155" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
@@ -4246,131 +4254,112 @@
         <v>8</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>12</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>361</v>
+        <v>8</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>329</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>415</v>
+        <v>383</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
+        <v>4</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
         <v>12</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>8</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>8</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>329</v>
+      <c r="B162" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>8</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>367</v>
+      <c r="B164" t="s">
+        <v>333</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>12</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>353</v>
+      <c r="B165" t="s">
+        <v>315</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>8</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>366</v>
+        <v>12</v>
+      </c>
+      <c r="B166" t="s">
+        <v>362</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
-        <v>8</v>
-      </c>
-      <c r="B173" t="s">
-        <v>333</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
         <v>12</v>
       </c>
-      <c r="B174" t="s">
-        <v>315</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
-        <v>12</v>
-      </c>
-      <c r="B175" t="s">
-        <v>362</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>416</v>
+      <c r="B167" t="s">
+        <v>52</v>
+      </c>
+      <c r="C167" t="s">
+        <v>53</v>
+      </c>
+      <c r="D167" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -4469,59 +4458,59 @@
     <hyperlink ref="C104" r:id="rId92" xr:uid="{0D69B397-D861-4A5D-9397-1BE272E25022}"/>
     <hyperlink ref="C105" r:id="rId93" xr:uid="{2C59DDBA-2D6F-4229-98AE-3A7C9586C72F}"/>
     <hyperlink ref="C106" r:id="rId94" xr:uid="{E63386B9-D4BB-4EC2-ABBC-787D5C433C84}"/>
-    <hyperlink ref="C111" r:id="rId95" xr:uid="{7B68E9DB-3F88-42AA-A5B8-6C92BC7CCC4A}"/>
-    <hyperlink ref="C109" r:id="rId96" xr:uid="{FD6CDB59-0FF2-404F-A390-575C163418DF}"/>
-    <hyperlink ref="C119" r:id="rId97" xr:uid="{E0FC33A2-D03A-48A6-87EF-59600AC38568}"/>
-    <hyperlink ref="C120" r:id="rId98" xr:uid="{0361F1EE-8DEC-4F6E-9D48-121367996FC4}"/>
-    <hyperlink ref="C121" r:id="rId99" xr:uid="{8A9E09A4-D03A-49DB-9C1D-2A335EBCA4F2}"/>
-    <hyperlink ref="C122" r:id="rId100" xr:uid="{AB242CEA-21F9-460F-898A-EA97DE8BE215}"/>
-    <hyperlink ref="C123" r:id="rId101" xr:uid="{FAC6DB05-5341-406B-A923-69D0A6A9F4CF}"/>
-    <hyperlink ref="C124" r:id="rId102" xr:uid="{A12DAF4F-DA53-4C37-A228-B06C66291FCE}"/>
-    <hyperlink ref="C125" r:id="rId103" xr:uid="{3802D333-ED18-449E-9357-390856F2E74F}"/>
-    <hyperlink ref="C126" r:id="rId104" xr:uid="{6DD592D8-7E8E-45B6-A26F-82CB136086DC}"/>
-    <hyperlink ref="C127" r:id="rId105" xr:uid="{687299CA-F5BD-4359-A19B-6739A9EB3A62}"/>
-    <hyperlink ref="C128" r:id="rId106" xr:uid="{9C01EF49-0F81-40FC-ACA2-1B5CEBEAF3C4}"/>
-    <hyperlink ref="C162" r:id="rId107" xr:uid="{A1ED9BDA-ACA5-4B6A-8562-F21A1133879C}"/>
-    <hyperlink ref="C129" r:id="rId108" xr:uid="{B6255BB1-281E-4413-AA60-7F650B88AE31}"/>
-    <hyperlink ref="C130" r:id="rId109" xr:uid="{5C4B4859-6F57-41C9-A767-78BAA0185AC6}"/>
-    <hyperlink ref="C173" r:id="rId110" xr:uid="{50F977BC-A580-40CA-99A8-12622C6DC83B}"/>
-    <hyperlink ref="C174" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
-    <hyperlink ref="C131" r:id="rId112" xr:uid="{812567D3-953B-4D03-AE8C-43607B67208C}"/>
-    <hyperlink ref="C132" r:id="rId113" xr:uid="{9F5366E7-2B07-4547-A415-A41154DAF6E8}"/>
-    <hyperlink ref="C133" r:id="rId114" xr:uid="{EC814759-6574-4DB1-9594-36303369F2E3}"/>
-    <hyperlink ref="C134" r:id="rId115" xr:uid="{DEB7B4FE-8BAA-4D7D-A585-E670B6B343C6}"/>
-    <hyperlink ref="C135" r:id="rId116" xr:uid="{7A6C01C3-E500-457E-82AF-768FAC2EE944}"/>
-    <hyperlink ref="C156" r:id="rId117" xr:uid="{AFBF2644-D248-411A-8729-0F8B67DA6166}"/>
-    <hyperlink ref="C157" r:id="rId118" xr:uid="{CF99D9B0-9ED1-49FE-BB38-F2FF4D60ED2D}"/>
-    <hyperlink ref="C136" r:id="rId119" xr:uid="{A48CD043-136D-4259-8BCF-9B9DD1903EBB}"/>
-    <hyperlink ref="C142" r:id="rId120" xr:uid="{81DE305D-88C6-4648-8210-032A2AB897D2}"/>
-    <hyperlink ref="C145" r:id="rId121" xr:uid="{AA4F5772-E99C-4FA5-8C55-0181B3B31431}"/>
-    <hyperlink ref="C147" r:id="rId122" xr:uid="{BB6B1DBE-0790-4C67-B2CD-03C5DF13EE91}"/>
-    <hyperlink ref="C152" r:id="rId123" xr:uid="{D7949A5B-0952-40E7-B0C6-1772D9DCD774}"/>
-    <hyperlink ref="C153" r:id="rId124" xr:uid="{2D3D6F71-FC76-4746-93A9-E61CEF274DF2}"/>
-    <hyperlink ref="C137" r:id="rId125" xr:uid="{E17CCA86-EE67-40CC-8E48-F995E9124648}"/>
-    <hyperlink ref="C138" r:id="rId126" xr:uid="{E62A1C12-A8AE-482B-86EA-0CEFC510063E}"/>
-    <hyperlink ref="C141" r:id="rId127" xr:uid="{135DD339-026F-4D89-8A58-A0DAC0070079}"/>
-    <hyperlink ref="C144" r:id="rId128" xr:uid="{CA906D41-EBEE-4DBF-AF9C-825A4EACE5D9}"/>
-    <hyperlink ref="C163" r:id="rId129" xr:uid="{2A4866D6-0938-4980-B2F8-C2D12CDF93FE}"/>
-    <hyperlink ref="C139" r:id="rId130" xr:uid="{944E35D1-9505-439F-B4D5-13DC55ECD476}"/>
-    <hyperlink ref="C140" r:id="rId131" xr:uid="{5CA067C0-559D-49DD-9CBC-05FF25FDB146}"/>
-    <hyperlink ref="C143" r:id="rId132" xr:uid="{146F583A-8654-483C-A3FE-787D22E6F0BF}"/>
-    <hyperlink ref="C146" r:id="rId133" xr:uid="{7657DEC4-1594-43D6-B1E6-AF7A3F185B0D}"/>
-    <hyperlink ref="C148" r:id="rId134" xr:uid="{7ECE2E4A-0794-46F4-ACC9-C940E483649D}"/>
-    <hyperlink ref="C155" r:id="rId135" xr:uid="{E7E53EF3-B599-4F18-B473-A861B6EC834C}"/>
-    <hyperlink ref="C165" r:id="rId136" xr:uid="{62F348E3-0B8D-47B6-8951-1599E9F9BD60}"/>
-    <hyperlink ref="C149" r:id="rId137" xr:uid="{0E01F3DE-80E8-4F2E-B432-B3737CFA4D99}"/>
-    <hyperlink ref="C150" r:id="rId138" xr:uid="{FA524709-47E9-490F-A089-312860B0DC84}"/>
-    <hyperlink ref="C151" r:id="rId139" xr:uid="{2478E041-032D-4CDD-A361-592BCEF9A589}"/>
-    <hyperlink ref="C154" r:id="rId140" xr:uid="{2C4DD23A-F9F2-479B-8C24-775407314589}"/>
-    <hyperlink ref="C158" r:id="rId141" xr:uid="{A75441B6-9439-4B62-8CA0-49107F5ED25F}"/>
-    <hyperlink ref="C159" r:id="rId142" xr:uid="{D1721C97-BCA6-44F5-AE02-814D7DCC88FB}"/>
-    <hyperlink ref="C175" r:id="rId143" xr:uid="{E0507AEA-A22E-45A8-AE1A-2EEE3DA0A0C9}"/>
-    <hyperlink ref="C160" r:id="rId144" xr:uid="{10462578-5E0B-41B2-8B9E-998C479B87AC}"/>
-    <hyperlink ref="C164" r:id="rId145" xr:uid="{71170706-AE5E-4242-AB9A-7D79E1339A5E}"/>
-    <hyperlink ref="C161" r:id="rId146" xr:uid="{DCBD3C2C-5441-4A9F-92FD-4B9D3CCF6F46}"/>
-    <hyperlink ref="C166" r:id="rId147" xr:uid="{36022F00-DC73-4627-8041-3B429A0E69A8}"/>
+    <hyperlink ref="C109" r:id="rId95" xr:uid="{7B68E9DB-3F88-42AA-A5B8-6C92BC7CCC4A}"/>
+    <hyperlink ref="C110" r:id="rId96" xr:uid="{FD6CDB59-0FF2-404F-A390-575C163418DF}"/>
+    <hyperlink ref="C116" r:id="rId97" xr:uid="{E0FC33A2-D03A-48A6-87EF-59600AC38568}"/>
+    <hyperlink ref="C117" r:id="rId98" xr:uid="{0361F1EE-8DEC-4F6E-9D48-121367996FC4}"/>
+    <hyperlink ref="C118" r:id="rId99" xr:uid="{8A9E09A4-D03A-49DB-9C1D-2A335EBCA4F2}"/>
+    <hyperlink ref="C119" r:id="rId100" xr:uid="{AB242CEA-21F9-460F-898A-EA97DE8BE215}"/>
+    <hyperlink ref="C120" r:id="rId101" xr:uid="{FAC6DB05-5341-406B-A923-69D0A6A9F4CF}"/>
+    <hyperlink ref="C121" r:id="rId102" xr:uid="{A12DAF4F-DA53-4C37-A228-B06C66291FCE}"/>
+    <hyperlink ref="C122" r:id="rId103" xr:uid="{3802D333-ED18-449E-9357-390856F2E74F}"/>
+    <hyperlink ref="C123" r:id="rId104" xr:uid="{6DD592D8-7E8E-45B6-A26F-82CB136086DC}"/>
+    <hyperlink ref="C124" r:id="rId105" xr:uid="{687299CA-F5BD-4359-A19B-6739A9EB3A62}"/>
+    <hyperlink ref="C125" r:id="rId106" xr:uid="{9C01EF49-0F81-40FC-ACA2-1B5CEBEAF3C4}"/>
+    <hyperlink ref="C159" r:id="rId107" xr:uid="{A1ED9BDA-ACA5-4B6A-8562-F21A1133879C}"/>
+    <hyperlink ref="C126" r:id="rId108" xr:uid="{B6255BB1-281E-4413-AA60-7F650B88AE31}"/>
+    <hyperlink ref="C127" r:id="rId109" xr:uid="{5C4B4859-6F57-41C9-A767-78BAA0185AC6}"/>
+    <hyperlink ref="C164" r:id="rId110" xr:uid="{50F977BC-A580-40CA-99A8-12622C6DC83B}"/>
+    <hyperlink ref="C165" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
+    <hyperlink ref="C128" r:id="rId112" xr:uid="{812567D3-953B-4D03-AE8C-43607B67208C}"/>
+    <hyperlink ref="C129" r:id="rId113" xr:uid="{9F5366E7-2B07-4547-A415-A41154DAF6E8}"/>
+    <hyperlink ref="C130" r:id="rId114" xr:uid="{EC814759-6574-4DB1-9594-36303369F2E3}"/>
+    <hyperlink ref="C131" r:id="rId115" xr:uid="{DEB7B4FE-8BAA-4D7D-A585-E670B6B343C6}"/>
+    <hyperlink ref="C132" r:id="rId116" xr:uid="{7A6C01C3-E500-457E-82AF-768FAC2EE944}"/>
+    <hyperlink ref="C153" r:id="rId117" xr:uid="{AFBF2644-D248-411A-8729-0F8B67DA6166}"/>
+    <hyperlink ref="C154" r:id="rId118" xr:uid="{CF99D9B0-9ED1-49FE-BB38-F2FF4D60ED2D}"/>
+    <hyperlink ref="C133" r:id="rId119" xr:uid="{A48CD043-136D-4259-8BCF-9B9DD1903EBB}"/>
+    <hyperlink ref="C139" r:id="rId120" xr:uid="{81DE305D-88C6-4648-8210-032A2AB897D2}"/>
+    <hyperlink ref="C142" r:id="rId121" xr:uid="{AA4F5772-E99C-4FA5-8C55-0181B3B31431}"/>
+    <hyperlink ref="C144" r:id="rId122" xr:uid="{BB6B1DBE-0790-4C67-B2CD-03C5DF13EE91}"/>
+    <hyperlink ref="C149" r:id="rId123" xr:uid="{D7949A5B-0952-40E7-B0C6-1772D9DCD774}"/>
+    <hyperlink ref="C150" r:id="rId124" xr:uid="{2D3D6F71-FC76-4746-93A9-E61CEF274DF2}"/>
+    <hyperlink ref="C134" r:id="rId125" xr:uid="{E17CCA86-EE67-40CC-8E48-F995E9124648}"/>
+    <hyperlink ref="C135" r:id="rId126" xr:uid="{E62A1C12-A8AE-482B-86EA-0CEFC510063E}"/>
+    <hyperlink ref="C138" r:id="rId127" xr:uid="{135DD339-026F-4D89-8A58-A0DAC0070079}"/>
+    <hyperlink ref="C141" r:id="rId128" xr:uid="{CA906D41-EBEE-4DBF-AF9C-825A4EACE5D9}"/>
+    <hyperlink ref="C160" r:id="rId129" xr:uid="{2A4866D6-0938-4980-B2F8-C2D12CDF93FE}"/>
+    <hyperlink ref="C136" r:id="rId130" xr:uid="{944E35D1-9505-439F-B4D5-13DC55ECD476}"/>
+    <hyperlink ref="C137" r:id="rId131" xr:uid="{5CA067C0-559D-49DD-9CBC-05FF25FDB146}"/>
+    <hyperlink ref="C140" r:id="rId132" xr:uid="{146F583A-8654-483C-A3FE-787D22E6F0BF}"/>
+    <hyperlink ref="C143" r:id="rId133" xr:uid="{7657DEC4-1594-43D6-B1E6-AF7A3F185B0D}"/>
+    <hyperlink ref="C145" r:id="rId134" xr:uid="{7ECE2E4A-0794-46F4-ACC9-C940E483649D}"/>
+    <hyperlink ref="C152" r:id="rId135" xr:uid="{E7E53EF3-B599-4F18-B473-A861B6EC834C}"/>
+    <hyperlink ref="C162" r:id="rId136" xr:uid="{62F348E3-0B8D-47B6-8951-1599E9F9BD60}"/>
+    <hyperlink ref="C146" r:id="rId137" xr:uid="{0E01F3DE-80E8-4F2E-B432-B3737CFA4D99}"/>
+    <hyperlink ref="C147" r:id="rId138" xr:uid="{FA524709-47E9-490F-A089-312860B0DC84}"/>
+    <hyperlink ref="C148" r:id="rId139" xr:uid="{2478E041-032D-4CDD-A361-592BCEF9A589}"/>
+    <hyperlink ref="C151" r:id="rId140" xr:uid="{2C4DD23A-F9F2-479B-8C24-775407314589}"/>
+    <hyperlink ref="C155" r:id="rId141" xr:uid="{A75441B6-9439-4B62-8CA0-49107F5ED25F}"/>
+    <hyperlink ref="C156" r:id="rId142" xr:uid="{D1721C97-BCA6-44F5-AE02-814D7DCC88FB}"/>
+    <hyperlink ref="C166" r:id="rId143" xr:uid="{E0507AEA-A22E-45A8-AE1A-2EEE3DA0A0C9}"/>
+    <hyperlink ref="C157" r:id="rId144" xr:uid="{10462578-5E0B-41B2-8B9E-998C479B87AC}"/>
+    <hyperlink ref="C161" r:id="rId145" xr:uid="{71170706-AE5E-4242-AB9A-7D79E1339A5E}"/>
+    <hyperlink ref="C158" r:id="rId146" xr:uid="{DCBD3C2C-5441-4A9F-92FD-4B9D3CCF6F46}"/>
+    <hyperlink ref="C163" r:id="rId147" xr:uid="{36022F00-DC73-4627-8041-3B429A0E69A8}"/>
     <hyperlink ref="C107" r:id="rId148" xr:uid="{3A053D4A-EB59-41B8-92A9-6039717F7935}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D15F0EA-5198-462D-94B3-AB06C83F2541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D496A8C8-D2C0-4950-95DA-2C333BB74E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="425">
   <si>
     <t>Difficulty</t>
   </si>
@@ -178,15 +178,9 @@
     <t>Array, Two Pointers, Sorting</t>
   </si>
   <si>
-    <t>Median of Two Sorted Arrays</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/median-of-two-sorted-arrays</t>
   </si>
   <si>
-    <t>Array, Binary Search, Divide and Conquer</t>
-  </si>
-  <si>
     <t>Maximum Subarray</t>
   </si>
   <si>
@@ -1298,6 +1292,9 @@
   </si>
   <si>
     <t>(PART-B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Median of Two Sorted Arrays</t>
   </si>
 </sst>
 </file>
@@ -2416,13 +2413,13 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
         <v>55</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -2430,13 +2427,13 @@
         <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
         <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -2444,13 +2441,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
         <v>61</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -2458,13 +2455,13 @@
         <v>8</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
         <v>64</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -2472,13 +2469,13 @@
         <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" t="s">
         <v>67</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -2486,10 +2483,10 @@
         <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
         <v>39</v>
@@ -2500,13 +2497,13 @@
         <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
         <v>72</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -2514,13 +2511,13 @@
         <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
         <v>75</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -2528,13 +2525,13 @@
         <v>8</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" t="s">
         <v>78</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -2542,13 +2539,13 @@
         <v>8</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" t="s">
         <v>81</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -2556,13 +2553,13 @@
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
         <v>84</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -2570,13 +2567,13 @@
         <v>8</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" t="s">
         <v>87</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -2584,13 +2581,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" t="s">
         <v>90</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -2598,13 +2595,13 @@
         <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" t="s">
         <v>93</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -2612,10 +2609,10 @@
         <v>12</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -2626,13 +2623,13 @@
         <v>12</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" t="s">
         <v>98</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -2640,13 +2637,13 @@
         <v>12</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" t="s">
         <v>101</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -2654,10 +2651,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
         <v>51</v>
@@ -2668,13 +2665,13 @@
         <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D34" t="s">
         <v>106</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D34" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -2682,13 +2679,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" t="s">
         <v>109</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -2696,13 +2693,13 @@
         <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" t="s">
         <v>112</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D36" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -2710,13 +2707,13 @@
         <v>8</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" t="s">
         <v>115</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -2724,13 +2721,13 @@
         <v>8</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" t="s">
+        <v>117</v>
+      </c>
+      <c r="D38" t="s">
         <v>118</v>
-      </c>
-      <c r="C38" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -2738,13 +2735,13 @@
         <v>8</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" t="s">
         <v>121</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -2752,13 +2749,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D40" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -2766,13 +2763,13 @@
         <v>8</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" t="s">
         <v>126</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -2780,13 +2777,13 @@
         <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" t="s">
         <v>129</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D42" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -2794,13 +2791,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" t="s">
         <v>132</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D43" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -2808,13 +2805,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" t="s">
         <v>135</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D44" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -2822,13 +2819,13 @@
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" t="s">
+        <v>137</v>
+      </c>
+      <c r="D45" t="s">
         <v>138</v>
-      </c>
-      <c r="C45" t="s">
-        <v>139</v>
-      </c>
-      <c r="D45" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -2836,13 +2833,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -2850,13 +2847,13 @@
         <v>8</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D47" t="s">
         <v>146</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D47" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -2864,13 +2861,13 @@
         <v>8</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D48" t="s">
         <v>149</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D48" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -2878,13 +2875,13 @@
         <v>8</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" t="s">
         <v>152</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D49" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -2892,13 +2889,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" t="s">
+        <v>154</v>
+      </c>
+      <c r="D50" t="s">
         <v>155</v>
-      </c>
-      <c r="C50" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -2906,13 +2903,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D51" t="s">
         <v>158</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D51" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -2920,13 +2917,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D52" t="s">
         <v>161</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D52" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -2934,13 +2931,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D53" t="s">
         <v>164</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D53" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -2948,10 +2945,10 @@
         <v>8</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D54" t="s">
         <v>39</v>
@@ -2962,13 +2959,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D55" t="s">
         <v>169</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D55" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -2976,13 +2973,13 @@
         <v>8</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D56" t="s">
         <v>172</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D56" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -2990,13 +2987,13 @@
         <v>8</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" t="s">
         <v>175</v>
-      </c>
-      <c r="C57" t="s">
-        <v>176</v>
-      </c>
-      <c r="D57" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -3004,13 +3001,13 @@
         <v>4</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D58" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
@@ -3018,13 +3015,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" t="s">
         <v>180</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D59" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -3032,10 +3029,10 @@
         <v>8</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D60" t="s">
         <v>39</v>
@@ -3046,13 +3043,13 @@
         <v>4</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" t="s">
         <v>185</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D61" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -3060,13 +3057,13 @@
         <v>8</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D62" t="s">
         <v>188</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D62" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -3074,13 +3071,13 @@
         <v>12</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D63" t="s">
         <v>191</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D63" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -3088,10 +3085,10 @@
         <v>8</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D64" t="s">
         <v>51</v>
@@ -3102,13 +3099,13 @@
         <v>8</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D65" t="s">
         <v>196</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D65" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
@@ -3116,13 +3113,13 @@
         <v>8</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D66" t="s">
         <v>199</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D66" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
@@ -3130,10 +3127,10 @@
         <v>8</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D67" t="s">
         <v>39</v>
@@ -3144,13 +3141,13 @@
         <v>8</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D68" t="s">
         <v>204</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D68" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
@@ -3158,10 +3155,10 @@
         <v>8</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D69" t="s">
         <v>33</v>
@@ -3172,10 +3169,10 @@
         <v>8</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D70" t="s">
         <v>51</v>
@@ -3186,13 +3183,13 @@
         <v>4</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D71" t="s">
         <v>211</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D71" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
@@ -3200,13 +3197,13 @@
         <v>4</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D72" t="s">
         <v>214</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D72" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
@@ -3214,13 +3211,13 @@
         <v>8</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D73" t="s">
         <v>220</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D73" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
@@ -3228,13 +3225,13 @@
         <v>8</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D74" t="s">
         <v>223</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D74" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
@@ -3242,13 +3239,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
@@ -3256,13 +3253,13 @@
         <v>8</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D76" t="s">
         <v>228</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D76" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
@@ -3270,13 +3267,13 @@
         <v>8</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D77" t="s">
         <v>231</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D77" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
@@ -3284,13 +3281,13 @@
         <v>8</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D78" t="s">
         <v>234</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D78" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
@@ -3298,13 +3295,13 @@
         <v>12</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D79" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
@@ -3312,13 +3309,13 @@
         <v>8</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D80" t="s">
         <v>245</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D80" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -3326,13 +3323,13 @@
         <v>8</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D81" t="s">
         <v>248</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D81" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
@@ -3340,13 +3337,13 @@
         <v>8</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D82" t="s">
         <v>251</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D82" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
@@ -3354,13 +3351,13 @@
         <v>8</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D83" t="s">
         <v>254</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D83" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
@@ -3368,13 +3365,13 @@
         <v>8</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D84" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
@@ -3382,13 +3379,13 @@
         <v>8</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D85" t="s">
         <v>259</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D85" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
@@ -3396,13 +3393,13 @@
         <v>8</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D86" t="s">
         <v>262</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D86" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
@@ -3410,13 +3407,13 @@
         <v>8</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D87" t="s">
         <v>265</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D87" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
@@ -3424,13 +3421,13 @@
         <v>8</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D88" t="s">
         <v>274</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D88" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
@@ -3438,13 +3435,13 @@
         <v>4</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D89" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
@@ -3452,13 +3449,13 @@
         <v>8</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D90" t="s">
         <v>281</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D90" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
@@ -3466,10 +3463,10 @@
         <v>4</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D91" t="s">
         <v>39</v>
@@ -3480,13 +3477,13 @@
         <v>8</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D92" t="s">
         <v>292</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D92" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
@@ -3494,10 +3491,10 @@
         <v>8</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
@@ -3508,13 +3505,13 @@
         <v>8</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D94" t="s">
         <v>300</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D94" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
@@ -3522,10 +3519,10 @@
         <v>8</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D95" t="s">
         <v>39</v>
@@ -3536,13 +3533,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D96" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
@@ -3550,13 +3547,13 @@
         <v>8</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D97" t="s">
         <v>307</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D97" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
@@ -3564,10 +3561,10 @@
         <v>12</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
@@ -3575,13 +3572,13 @@
         <v>8</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D99" t="s">
         <v>217</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D99" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
@@ -3589,13 +3586,13 @@
         <v>8</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100" t="s">
         <v>239</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D100" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
@@ -3603,13 +3600,13 @@
         <v>8</v>
       </c>
       <c r="B101" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D101" t="s">
         <v>268</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D101" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
@@ -3617,13 +3614,13 @@
         <v>8</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D102" t="s">
         <v>271</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D102" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
@@ -3631,13 +3628,13 @@
         <v>8</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D103" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
@@ -3645,13 +3642,13 @@
         <v>8</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D104" t="s">
         <v>284</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D104" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
@@ -3659,13 +3656,13 @@
         <v>8</v>
       </c>
       <c r="B105" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D105" t="s">
         <v>289</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D105" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
@@ -3673,13 +3670,13 @@
         <v>8</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D106" t="s">
         <v>297</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D106" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
@@ -3701,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D108" t="s">
         <v>143</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D108" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
@@ -3715,32 +3712,32 @@
         <v>12</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D109" t="s">
         <v>310</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D109" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>8</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D110" t="s">
         <v>242</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D110" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B111" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
@@ -3748,10 +3745,10 @@
         <v>8</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C112" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
@@ -3759,10 +3756,10 @@
         <v>8</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C113" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
@@ -3770,10 +3767,10 @@
         <v>8</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C114" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
@@ -3781,10 +3778,10 @@
         <v>12</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C115" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
@@ -3792,10 +3789,10 @@
         <v>12</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
@@ -3803,10 +3800,10 @@
         <v>8</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
@@ -3814,10 +3811,10 @@
         <v>8</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
@@ -3825,10 +3822,10 @@
         <v>8</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
@@ -3836,10 +3833,10 @@
         <v>4</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
@@ -3847,10 +3844,10 @@
         <v>8</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
@@ -3858,10 +3855,10 @@
         <v>8</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
@@ -3869,10 +3866,10 @@
         <v>8</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
@@ -3880,10 +3877,10 @@
         <v>8</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
@@ -3891,10 +3888,10 @@
         <v>4</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
@@ -3902,10 +3899,10 @@
         <v>8</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
@@ -3913,10 +3910,10 @@
         <v>8</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
@@ -3924,10 +3921,10 @@
         <v>8</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
@@ -3935,10 +3932,10 @@
         <v>8</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
@@ -3946,10 +3943,10 @@
         <v>8</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
@@ -3957,10 +3954,10 @@
         <v>8</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
@@ -3968,10 +3965,10 @@
         <v>4</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
@@ -3979,10 +3976,10 @@
         <v>8</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
@@ -3990,10 +3987,10 @@
         <v>8</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
@@ -4001,10 +3998,10 @@
         <v>8</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
@@ -4012,10 +4009,10 @@
         <v>4</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
@@ -4023,10 +4020,10 @@
         <v>4</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
@@ -4034,10 +4031,10 @@
         <v>4</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
@@ -4045,10 +4042,10 @@
         <v>12</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
@@ -4056,10 +4053,10 @@
         <v>12</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -4067,10 +4064,10 @@
         <v>8</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
@@ -4078,10 +4075,10 @@
         <v>4</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -4089,10 +4086,10 @@
         <v>12</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
@@ -4100,10 +4097,10 @@
         <v>4</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
@@ -4111,10 +4108,10 @@
         <v>4</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
@@ -4122,10 +4119,10 @@
         <v>8</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
@@ -4133,10 +4130,10 @@
         <v>8</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
@@ -4144,10 +4141,10 @@
         <v>8</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
@@ -4155,10 +4152,10 @@
         <v>4</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -4166,10 +4163,10 @@
         <v>4</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -4177,10 +4174,10 @@
         <v>8</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -4188,10 +4185,10 @@
         <v>8</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
@@ -4199,10 +4196,10 @@
         <v>8</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
@@ -4210,10 +4207,10 @@
         <v>8</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
@@ -4221,10 +4218,10 @@
         <v>8</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
@@ -4232,10 +4229,10 @@
         <v>12</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
@@ -4243,10 +4240,10 @@
         <v>12</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
@@ -4254,10 +4251,10 @@
         <v>8</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
@@ -4265,10 +4262,10 @@
         <v>8</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
@@ -4276,90 +4273,87 @@
         <v>4</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>8</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>12</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>8</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>12</v>
       </c>
       <c r="B167" t="s">
+        <v>424</v>
+      </c>
+      <c r="C167" t="s">
         <v>52</v>
-      </c>
-      <c r="C167" t="s">
-        <v>53</v>
-      </c>
-      <c r="D167" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D496A8C8-D2C0-4950-95DA-2C333BB74E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A70FF0-AA7E-4C0D-BA0A-DFAED03C0795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -2821,7 +2821,7 @@
       <c r="B45" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="2" t="s">
         <v>137</v>
       </c>
       <c r="D45" t="s">
@@ -3224,7 +3224,7 @@
       <c r="A74" t="s">
         <v>8</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="5" t="s">
         <v>221</v>
       </c>
       <c r="C74" s="2" t="s">
@@ -4506,8 +4506,9 @@
     <hyperlink ref="C158" r:id="rId146" xr:uid="{DCBD3C2C-5441-4A9F-92FD-4B9D3CCF6F46}"/>
     <hyperlink ref="C163" r:id="rId147" xr:uid="{36022F00-DC73-4627-8041-3B429A0E69A8}"/>
     <hyperlink ref="C107" r:id="rId148" xr:uid="{3A053D4A-EB59-41B8-92A9-6039717F7935}"/>
+    <hyperlink ref="C45" r:id="rId149" xr:uid="{A10388A2-D172-4BDE-9B3B-630EF54F1CB1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId149"/>
+  <pageSetup orientation="portrait" r:id="rId150"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A70FF0-AA7E-4C0D-BA0A-DFAED03C0795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6478A3B-D72C-4E5B-8EB7-1DC136D06FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -3613,7 +3613,7 @@
       <c r="A102" t="s">
         <v>8</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="5" t="s">
         <v>269</v>
       </c>
       <c r="C102" s="2" t="s">
@@ -3641,7 +3641,7 @@
       <c r="A104" t="s">
         <v>8</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="5" t="s">
         <v>282</v>
       </c>
       <c r="C104" s="2" t="s">
@@ -3747,7 +3747,7 @@
       <c r="B112" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="2" t="s">
         <v>369</v>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       <c r="B113" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="2" t="s">
         <v>375</v>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       <c r="B114" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="2" t="s">
         <v>373</v>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       <c r="B115" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="2" t="s">
         <v>382</v>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       <c r="A122" t="s">
         <v>8</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="5" t="s">
         <v>314</v>
       </c>
       <c r="C122" s="2" t="s">
@@ -3964,7 +3964,7 @@
       <c r="A132" t="s">
         <v>4</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B132" s="5" t="s">
         <v>336</v>
       </c>
       <c r="C132" s="2" t="s">
@@ -4507,8 +4507,12 @@
     <hyperlink ref="C163" r:id="rId147" xr:uid="{36022F00-DC73-4627-8041-3B429A0E69A8}"/>
     <hyperlink ref="C107" r:id="rId148" xr:uid="{3A053D4A-EB59-41B8-92A9-6039717F7935}"/>
     <hyperlink ref="C45" r:id="rId149" xr:uid="{A10388A2-D172-4BDE-9B3B-630EF54F1CB1}"/>
+    <hyperlink ref="C112" r:id="rId150" xr:uid="{5E16A982-6CA6-4B83-87DB-51C87C4B5F38}"/>
+    <hyperlink ref="C113" r:id="rId151" xr:uid="{582F451E-1600-47ED-BE40-CE7AE76AB856}"/>
+    <hyperlink ref="C114" r:id="rId152" xr:uid="{45A1DCE2-895B-4281-8D16-DB41A58F6E4F}"/>
+    <hyperlink ref="C115" r:id="rId153" xr:uid="{02881D8B-9944-4A49-AB95-663A32B8C1A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId150"/>
+  <pageSetup orientation="portrait" r:id="rId154"/>
 </worksheet>
 </file>
--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6478A3B-D72C-4E5B-8EB7-1DC136D06FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFEFB18-049B-4CBC-8967-DB88564D44E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -4107,7 +4107,7 @@
       <c r="A145" t="s">
         <v>4</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B145" s="5" t="s">
         <v>350</v>
       </c>
       <c r="C145" s="2" t="s">
@@ -4162,7 +4162,7 @@
       <c r="A150" t="s">
         <v>4</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B150" s="5" t="s">
         <v>356</v>
       </c>
       <c r="C150" s="2" t="s">
@@ -4316,7 +4316,7 @@
       <c r="A164" t="s">
         <v>8</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164" s="1" t="s">
         <v>331</v>
       </c>
       <c r="C164" s="2" t="s">

--- a/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
+++ b/AmazonRecentInterviewQuestions/amazon_sde1_filtered_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\AmazonRecentInterviewQuestions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFEFB18-049B-4CBC-8967-DB88564D44E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97861BF-658B-458D-B1A5-1A4B6A495BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{57A929C8-930A-4808-BFA1-E940B7892482}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="427">
   <si>
     <t>Difficulty</t>
   </si>
@@ -1295,6 +1295,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Median of Two Sorted Arrays</t>
+  </si>
+  <si>
+    <t>Path with Minimum Effort</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/path-with-minimum-effort/description/</t>
   </si>
 </sst>
 </file>
@@ -1807,11 +1813,11 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2188,7 +2194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C267225-C50B-440B-AFF3-5C88037D1483}">
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
@@ -2199,16 +2205,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2216,10 +2222,10 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
@@ -2230,10 +2236,10 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
@@ -2244,10 +2250,10 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
@@ -2258,10 +2264,10 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D5" t="s">
@@ -2272,10 +2278,10 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
@@ -2286,10 +2292,10 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D7" t="s">
@@ -2300,10 +2306,10 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
@@ -2314,10 +2320,10 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D9" t="s">
@@ -2328,10 +2334,10 @@
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="s">
@@ -2342,10 +2348,10 @@
       <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D11" t="s">
@@ -2356,10 +2362,10 @@
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D12" t="s">
@@ -2370,10 +2376,10 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D13" t="s">
@@ -2384,10 +2390,10 @@
       <c r="A14" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D14" t="s">
@@ -2398,10 +2404,10 @@
       <c r="A15" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D15" t="s">
@@ -2412,10 +2418,10 @@
       <c r="A16" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D16" t="s">
@@ -2426,10 +2432,10 @@
       <c r="A17" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D17" t="s">
@@ -2440,10 +2446,10 @@
       <c r="A18" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D18" t="s">
@@ -2454,10 +2460,10 @@
       <c r="A19" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D19" t="s">
@@ -2468,10 +2474,10 @@
       <c r="A20" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D20" t="s">
@@ -2482,10 +2488,10 @@
       <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D21" t="s">
@@ -2496,10 +2502,10 @@
       <c r="A22" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>71</v>
       </c>
       <c r="D22" t="s">
@@ -2510,10 +2516,10 @@
       <c r="A23" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D23" t="s">
@@ -2524,10 +2530,10 @@
       <c r="A24" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D24" t="s">
@@ -2538,10 +2544,10 @@
       <c r="A25" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D25" t="s">
@@ -2552,10 +2558,10 @@
       <c r="A26" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>83</v>
       </c>
       <c r="D26" t="s">
@@ -2566,10 +2572,10 @@
       <c r="A27" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>86</v>
       </c>
       <c r="D27" t="s">
@@ -2580,10 +2586,10 @@
       <c r="A28" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>89</v>
       </c>
       <c r="D28" t="s">
@@ -2594,10 +2600,10 @@
       <c r="A29" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>92</v>
       </c>
       <c r="D29" t="s">
@@ -2608,10 +2614,10 @@
       <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D30" t="s">
@@ -2622,10 +2628,10 @@
       <c r="A31" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>97</v>
       </c>
       <c r="D31" t="s">
@@ -2636,10 +2642,10 @@
       <c r="A32" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>100</v>
       </c>
       <c r="D32" t="s">
@@ -2650,10 +2656,10 @@
       <c r="A33" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="3" t="s">
         <v>103</v>
       </c>
       <c r="D33" t="s">
@@ -2664,10 +2670,10 @@
       <c r="A34" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>105</v>
       </c>
       <c r="D34" t="s">
@@ -2678,10 +2684,10 @@
       <c r="A35" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="3" t="s">
         <v>108</v>
       </c>
       <c r="D35" t="s">
@@ -2692,10 +2698,10 @@
       <c r="A36" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D36" t="s">
@@ -2706,10 +2712,10 @@
       <c r="A37" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="3" t="s">
         <v>114</v>
       </c>
       <c r="D37" t="s">
@@ -2720,10 +2726,10 @@
       <c r="A38" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D38" t="s">
@@ -2734,10 +2740,10 @@
       <c r="A39" t="s">
         <v>8</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D39" t="s">
@@ -2748,10 +2754,10 @@
       <c r="A40" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="3" t="s">
         <v>123</v>
       </c>
       <c r="D40" t="s">
@@ -2762,10 +2768,10 @@
       <c r="A41" t="s">
         <v>8</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D41" t="s">
@@ -2776,10 +2782,10 @@
       <c r="A42" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D42" t="s">
@@ -2790,10 +2796,10 @@
       <c r="A43" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="3" t="s">
         <v>131</v>
       </c>
       <c r="D43" t="s">
@@ -2804,10 +2810,10 @@
       <c r="A44" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="3" t="s">
         <v>134</v>
       </c>
       <c r="D44" t="s">
@@ -2818,10 +2824,10 @@
       <c r="A45" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D45" t="s">
@@ -2832,10 +2838,10 @@
       <c r="A46" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D46" t="s">
@@ -2846,10 +2852,10 @@
       <c r="A47" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="3" t="s">
         <v>145</v>
       </c>
       <c r="D47" t="s">
@@ -2860,10 +2866,10 @@
       <c r="A48" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="3" t="s">
         <v>148</v>
       </c>
       <c r="D48" t="s">
@@ -2874,10 +2880,10 @@
       <c r="A49" t="s">
         <v>8</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="3" t="s">
         <v>151</v>
       </c>
       <c r="D49" t="s">
@@ -2888,7 +2894,7 @@
       <c r="A50" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C50" t="s">
@@ -2902,10 +2908,10 @@
       <c r="A51" t="s">
         <v>4</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D51" t="s">
@@ -2916,10 +2922,10 @@
       <c r="A52" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="3" t="s">
         <v>160</v>
       </c>
       <c r="D52" t="s">
@@ -2930,10 +2936,10 @@
       <c r="A53" t="s">
         <v>4</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="3" t="s">
         <v>163</v>
       </c>
       <c r="D53" t="s">
@@ -2944,10 +2950,10 @@
       <c r="A54" t="s">
         <v>8</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="3" t="s">
         <v>166</v>
       </c>
       <c r="D54" t="s">
@@ -2958,10 +2964,10 @@
       <c r="A55" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D55" t="s">
@@ -2972,10 +2978,10 @@
       <c r="A56" t="s">
         <v>8</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="3" t="s">
         <v>171</v>
       </c>
       <c r="D56" t="s">
@@ -2986,7 +2992,7 @@
       <c r="A57" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C57" t="s">
@@ -3000,10 +3006,10 @@
       <c r="A58" t="s">
         <v>4</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="3" t="s">
         <v>177</v>
       </c>
       <c r="D58" t="s">
@@ -3014,10 +3020,10 @@
       <c r="A59" t="s">
         <v>8</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="3" t="s">
         <v>179</v>
       </c>
       <c r="D59" t="s">
@@ -3028,10 +3034,10 @@
       <c r="A60" t="s">
         <v>8</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="3" t="s">
         <v>182</v>
       </c>
       <c r="D60" t="s">
@@ -3042,10 +3048,10 @@
       <c r="A61" t="s">
         <v>4</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="3" t="s">
         <v>184</v>
       </c>
       <c r="D61" t="s">
@@ -3056,10 +3062,10 @@
       <c r="A62" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="3" t="s">
         <v>187</v>
       </c>
       <c r="D62" t="s">
@@ -3070,10 +3076,10 @@
       <c r="A63" t="s">
         <v>12</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D63" t="s">
@@ -3084,10 +3090,10 @@
       <c r="A64" t="s">
         <v>8</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="3" t="s">
         <v>193</v>
       </c>
       <c r="D64" t="s">
@@ -3098,10 +3104,10 @@
       <c r="A65" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D65" t="s">
@@ -3112,10 +3118,10 @@
       <c r="A66" t="s">
         <v>8</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="3" t="s">
         <v>198</v>
       </c>
       <c r="D66" t="s">
@@ -3126,10 +3132,10 @@
       <c r="A67" t="s">
         <v>8</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="3" t="s">
         <v>201</v>
       </c>
       <c r="D67" t="s">
@@ -3140,10 +3146,10 @@
       <c r="A68" t="s">
         <v>8</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="3" t="s">
         <v>203</v>
       </c>
       <c r="D68" t="s">
@@ -3154,10 +3160,10 @@
       <c r="A69" t="s">
         <v>8</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="3" t="s">
         <v>206</v>
       </c>
       <c r="D69" t="s">
@@ -3168,10 +3174,10 @@
       <c r="A70" t="s">
         <v>8</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="3" t="s">
         <v>208</v>
       </c>
       <c r="D70" t="s">
@@ -3182,10 +3188,10 @@
       <c r="A71" t="s">
         <v>4</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="3" t="s">
         <v>210</v>
       </c>
       <c r="D71" t="s">
@@ -3196,10 +3202,10 @@
       <c r="A72" t="s">
         <v>4</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="3" t="s">
         <v>213</v>
       </c>
       <c r="D72" t="s">
@@ -3210,10 +3216,10 @@
       <c r="A73" t="s">
         <v>8</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D73" t="s">
@@ -3224,10 +3230,10 @@
       <c r="A74" t="s">
         <v>8</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="3" t="s">
         <v>222</v>
       </c>
       <c r="D74" t="s">
@@ -3238,10 +3244,10 @@
       <c r="A75" t="s">
         <v>8</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="3" t="s">
         <v>225</v>
       </c>
       <c r="D75" t="s">
@@ -3252,10 +3258,10 @@
       <c r="A76" t="s">
         <v>8</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="3" t="s">
         <v>227</v>
       </c>
       <c r="D76" t="s">
@@ -3266,10 +3272,10 @@
       <c r="A77" t="s">
         <v>8</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D77" t="s">
@@ -3280,10 +3286,10 @@
       <c r="A78" t="s">
         <v>8</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="3" t="s">
         <v>233</v>
       </c>
       <c r="D78" t="s">
@@ -3294,10 +3300,10 @@
       <c r="A79" t="s">
         <v>12</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="3" t="s">
         <v>236</v>
       </c>
       <c r="D79" t="s">
@@ -3308,10 +3314,10 @@
       <c r="A80" t="s">
         <v>8</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="3" t="s">
         <v>244</v>
       </c>
       <c r="D80" t="s">
@@ -3322,10 +3328,10 @@
       <c r="A81" t="s">
         <v>8</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="3" t="s">
         <v>247</v>
       </c>
       <c r="D81" t="s">
@@ -3336,10 +3342,10 @@
       <c r="A82" t="s">
         <v>8</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D82" t="s">
@@ -3350,10 +3356,10 @@
       <c r="A83" t="s">
         <v>8</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="3" t="s">
         <v>253</v>
       </c>
       <c r="D83" t="s">
@@ -3364,10 +3370,10 @@
       <c r="A84" t="s">
         <v>8</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="3" t="s">
         <v>256</v>
       </c>
       <c r="D84" t="s">
@@ -3378,10 +3384,10 @@
       <c r="A85" t="s">
         <v>8</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="3" t="s">
         <v>258</v>
       </c>
       <c r="D85" t="s">
@@ -3392,10 +3398,10 @@
       <c r="A86" t="s">
         <v>8</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="3" t="s">
         <v>261</v>
       </c>
       <c r="D86" t="s">
@@ -3406,10 +3412,10 @@
       <c r="A87" t="s">
         <v>8</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="3" t="s">
         <v>264</v>
       </c>
       <c r="D87" t="s">
@@ -3420,10 +3426,10 @@
       <c r="A88" t="s">
         <v>8</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="3" t="s">
         <v>273</v>
       </c>
       <c r="D88" t="s">
@@ -3434,10 +3440,10 @@
       <c r="A89" t="s">
         <v>4</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="3" t="s">
         <v>278</v>
       </c>
       <c r="D89" t="s">
@@ -3448,10 +3454,10 @@
       <c r="A90" t="s">
         <v>8</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="3" t="s">
         <v>280</v>
       </c>
       <c r="D90" t="s">
@@ -3462,10 +3468,10 @@
       <c r="A91" t="s">
         <v>4</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="3" t="s">
         <v>286</v>
       </c>
       <c r="D91" t="s">
@@ -3476,10 +3482,10 @@
       <c r="A92" t="s">
         <v>8</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="3" t="s">
         <v>291</v>
       </c>
       <c r="D92" t="s">
@@ -3490,10 +3496,10 @@
       <c r="A93" t="s">
         <v>8</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="3" t="s">
         <v>294</v>
       </c>
       <c r="D93" t="s">
@@ -3504,10 +3510,10 @@
       <c r="A94" t="s">
         <v>8</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="3" t="s">
         <v>299</v>
       </c>
       <c r="D94" t="s">
@@ -3518,10 +3524,10 @@
       <c r="A95" t="s">
         <v>8</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="3" t="s">
         <v>302</v>
       </c>
       <c r="D95" t="s">
@@ -3532,10 +3538,10 @@
       <c r="A96" t="s">
         <v>4</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="3" t="s">
         <v>304</v>
       </c>
       <c r="D96" t="s">
@@ -3546,10 +3552,10 @@
       <c r="A97" t="s">
         <v>8</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="3" t="s">
         <v>306</v>
       </c>
       <c r="D97" t="s">
@@ -3560,10 +3566,10 @@
       <c r="A98" t="s">
         <v>12</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="3" t="s">
         <v>312</v>
       </c>
     </row>
@@ -3571,10 +3577,10 @@
       <c r="A99" t="s">
         <v>8</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="3" t="s">
         <v>216</v>
       </c>
       <c r="D99" t="s">
@@ -3585,10 +3591,10 @@
       <c r="A100" t="s">
         <v>8</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="3" t="s">
         <v>238</v>
       </c>
       <c r="D100" t="s">
@@ -3599,10 +3605,10 @@
       <c r="A101" t="s">
         <v>8</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="3" t="s">
         <v>267</v>
       </c>
       <c r="D101" t="s">
@@ -3613,10 +3619,10 @@
       <c r="A102" t="s">
         <v>8</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="3" t="s">
         <v>270</v>
       </c>
       <c r="D102" t="s">
@@ -3627,10 +3633,10 @@
       <c r="A103" t="s">
         <v>8</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="3" t="s">
         <v>276</v>
       </c>
       <c r="D103" t="s">
@@ -3641,10 +3647,10 @@
       <c r="A104" t="s">
         <v>8</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="3" t="s">
         <v>283</v>
       </c>
       <c r="D104" t="s">
@@ -3655,10 +3661,10 @@
       <c r="A105" t="s">
         <v>8</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="3" t="s">
         <v>288</v>
       </c>
       <c r="D105" t="s">
@@ -3669,10 +3675,10 @@
       <c r="A106" t="s">
         <v>8</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="3" t="s">
         <v>296</v>
       </c>
       <c r="D106" t="s">
@@ -3683,10 +3689,10 @@
       <c r="A107" t="s">
         <v>8</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B107" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D107" t="s">
@@ -3697,10 +3703,10 @@
       <c r="A108" t="s">
         <v>8</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B108" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="3" t="s">
         <v>142</v>
       </c>
       <c r="D108" t="s">
@@ -3711,10 +3717,10 @@
       <c r="A109" t="s">
         <v>12</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="3" t="s">
         <v>309</v>
       </c>
       <c r="D109" t="s">
@@ -3725,10 +3731,10 @@
       <c r="A110" t="s">
         <v>8</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="3" t="s">
         <v>241</v>
       </c>
       <c r="D110" t="s">
@@ -3736,7 +3742,7 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="1" t="s">
         <v>423</v>
       </c>
     </row>
@@ -3744,10 +3750,10 @@
       <c r="A112" t="s">
         <v>8</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="3" t="s">
         <v>369</v>
       </c>
     </row>
@@ -3755,10 +3761,10 @@
       <c r="A113" t="s">
         <v>8</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="3" t="s">
         <v>375</v>
       </c>
     </row>
@@ -3766,10 +3772,10 @@
       <c r="A114" t="s">
         <v>8</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="3" t="s">
         <v>373</v>
       </c>
     </row>
@@ -3777,10 +3783,10 @@
       <c r="A115" t="s">
         <v>12</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="3" t="s">
         <v>382</v>
       </c>
     </row>
@@ -3788,10 +3794,10 @@
       <c r="A116" t="s">
         <v>12</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="3" t="s">
         <v>370</v>
       </c>
     </row>
@@ -3799,10 +3805,10 @@
       <c r="A117" t="s">
         <v>8</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="3" t="s">
         <v>371</v>
       </c>
     </row>
@@ -3810,10 +3816,10 @@
       <c r="A118" t="s">
         <v>8</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="3" t="s">
         <v>372</v>
       </c>
     </row>
@@ -3821,10 +3827,10 @@
       <c r="A119" t="s">
         <v>8</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="3" t="s">
         <v>374</v>
       </c>
     </row>
@@ -3832,10 +3838,10 @@
       <c r="A120" t="s">
         <v>4</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="3" t="s">
         <v>376</v>
       </c>
     </row>
@@ -3843,10 +3849,10 @@
       <c r="A121" t="s">
         <v>8</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="3" t="s">
         <v>377</v>
       </c>
     </row>
@@ -3854,10 +3860,10 @@
       <c r="A122" t="s">
         <v>8</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B122" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="3" t="s">
         <v>368</v>
       </c>
     </row>
@@ -3865,10 +3871,10 @@
       <c r="A123" t="s">
         <v>8</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C123" s="3" t="s">
         <v>378</v>
       </c>
     </row>
@@ -3876,10 +3882,10 @@
       <c r="A124" t="s">
         <v>8</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="C124" s="3" t="s">
         <v>379</v>
       </c>
     </row>
@@ -3887,10 +3893,10 @@
       <c r="A125" t="s">
         <v>4</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="C125" s="3" t="s">
         <v>380</v>
       </c>
     </row>
@@ -3898,10 +3904,10 @@
       <c r="A126" t="s">
         <v>8</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="3" t="s">
         <v>383</v>
       </c>
     </row>
@@ -3909,10 +3915,10 @@
       <c r="A127" t="s">
         <v>8</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="C127" s="3" t="s">
         <v>384</v>
       </c>
     </row>
@@ -3920,10 +3926,10 @@
       <c r="A128" t="s">
         <v>8</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="3" t="s">
         <v>386</v>
       </c>
     </row>
@@ -3931,10 +3937,10 @@
       <c r="A129" t="s">
         <v>8</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B129" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="C129" s="3" t="s">
         <v>387</v>
       </c>
     </row>
@@ -3942,10 +3948,10 @@
       <c r="A130" t="s">
         <v>8</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B130" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="3" t="s">
         <v>388</v>
       </c>
     </row>
@@ -3953,10 +3959,10 @@
       <c r="A131" t="s">
         <v>8</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B131" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C131" s="3" t="s">
         <v>389</v>
       </c>
     </row>
@@ -3964,10 +3970,10 @@
       <c r="A132" t="s">
         <v>4</v>
       </c>
-      <c r="B132" s="5" t="s">
+      <c r="B132" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C132" s="3" t="s">
         <v>390</v>
       </c>
     </row>
@@ -3975,10 +3981,10 @@
       <c r="A133" t="s">
         <v>8</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B133" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C133" s="3" t="s">
         <v>396</v>
       </c>
     </row>
@@ -3986,10 +3992,10 @@
       <c r="A134" t="s">
         <v>8</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B134" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="3" t="s">
         <v>411</v>
       </c>
     </row>
@@ -3997,10 +4003,10 @@
       <c r="A135" t="s">
         <v>8</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B135" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C135" s="3" t="s">
         <v>417</v>
       </c>
     </row>
@@ -4008,10 +4014,10 @@
       <c r="A136" t="s">
         <v>4</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B136" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C136" s="2" t="s">
+      <c r="C136" s="3" t="s">
         <v>395</v>
       </c>
     </row>
@@ -4019,10 +4025,10 @@
       <c r="A137" t="s">
         <v>4</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B137" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C137" s="3" t="s">
         <v>397</v>
       </c>
     </row>
@@ -4030,10 +4036,10 @@
       <c r="A138" t="s">
         <v>4</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B138" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="3" t="s">
         <v>416</v>
       </c>
     </row>
@@ -4041,10 +4047,10 @@
       <c r="A139" t="s">
         <v>12</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B139" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C139" s="2" t="s">
+      <c r="C139" s="3" t="s">
         <v>398</v>
       </c>
     </row>
@@ -4052,10 +4058,10 @@
       <c r="A140" t="s">
         <v>12</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B140" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C140" s="3" t="s">
         <v>399</v>
       </c>
     </row>
@@ -4063,10 +4069,10 @@
       <c r="A141" t="s">
         <v>8</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B141" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="C141" s="3" t="s">
         <v>420</v>
       </c>
     </row>
@@ -4074,10 +4080,10 @@
       <c r="A142" t="s">
         <v>4</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B142" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="3" t="s">
         <v>401</v>
       </c>
     </row>
@@ -4085,10 +4091,10 @@
       <c r="A143" t="s">
         <v>12</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B143" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C143" s="3" t="s">
         <v>400</v>
       </c>
     </row>
@@ -4096,10 +4102,10 @@
       <c r="A144" t="s">
         <v>4</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="3" t="s">
         <v>403</v>
       </c>
     </row>
@@ -4107,10 +4113,10 @@
       <c r="A145" t="s">
         <v>4</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="B145" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C145" s="3" t="s">
         <v>404</v>
       </c>
     </row>
@@ -4118,10 +4124,10 @@
       <c r="A146" t="s">
         <v>8</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B146" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="3" t="s">
         <v>406</v>
       </c>
     </row>
@@ -4129,10 +4135,10 @@
       <c r="A147" t="s">
         <v>8</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B147" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C147" s="3" t="s">
         <v>408</v>
       </c>
     </row>
@@ -4140,10 +4146,10 @@
       <c r="A148" t="s">
         <v>8</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B148" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C148" s="3" t="s">
         <v>422</v>
       </c>
     </row>
@@ -4151,10 +4157,10 @@
       <c r="A149" t="s">
         <v>4</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="B149" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C149" s="3" t="s">
         <v>407</v>
       </c>
     </row>
@@ -4162,10 +4168,10 @@
       <c r="A150" t="s">
         <v>4</v>
       </c>
-      <c r="B150" s="5" t="s">
+      <c r="B150" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="3" t="s">
         <v>410</v>
       </c>
     </row>
@@ -4173,10 +4179,10 @@
       <c r="A151" t="s">
         <v>8</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B151" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="3" t="s">
         <v>409</v>
       </c>
     </row>
@@ -4184,10 +4190,10 @@
       <c r="A152" t="s">
         <v>8</v>
       </c>
-      <c r="B152" s="5" t="s">
+      <c r="B152" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="3" t="s">
         <v>402</v>
       </c>
     </row>
@@ -4195,10 +4201,10 @@
       <c r="A153" t="s">
         <v>8</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="B153" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="C153" s="3" t="s">
         <v>391</v>
       </c>
     </row>
@@ -4206,10 +4212,10 @@
       <c r="A154" t="s">
         <v>8</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B154" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="3" t="s">
         <v>392</v>
       </c>
     </row>
@@ -4217,10 +4223,10 @@
       <c r="A155" t="s">
         <v>8</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B155" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C155" s="3" t="s">
         <v>412</v>
       </c>
     </row>
@@ -4228,10 +4234,10 @@
       <c r="A156" t="s">
         <v>12</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B156" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C156" s="3" t="s">
         <v>413</v>
       </c>
     </row>
@@ -4239,10 +4245,10 @@
       <c r="A157" t="s">
         <v>12</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B157" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C157" s="3" t="s">
         <v>415</v>
       </c>
     </row>
@@ -4250,10 +4256,10 @@
       <c r="A158" t="s">
         <v>8</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="B158" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="3" t="s">
         <v>393</v>
       </c>
     </row>
@@ -4261,10 +4267,10 @@
       <c r="A159" t="s">
         <v>8</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="B159" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="3" t="s">
         <v>381</v>
       </c>
     </row>
@@ -4272,10 +4278,10 @@
       <c r="A160" t="s">
         <v>4</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="B160" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="3" t="s">
         <v>394</v>
       </c>
     </row>
@@ -4283,10 +4289,10 @@
       <c r="A161" t="s">
         <v>8</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="B161" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C161" s="3" t="s">
         <v>419</v>
       </c>
     </row>
@@ -4294,10 +4300,10 @@
       <c r="A162" t="s">
         <v>12</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B162" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="3" t="s">
         <v>405</v>
       </c>
     </row>
@@ -4305,10 +4311,10 @@
       <c r="A163" t="s">
         <v>8</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B163" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C163" s="3" t="s">
         <v>418</v>
       </c>
     </row>
@@ -4316,22 +4322,22 @@
       <c r="A164" t="s">
         <v>8</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B164" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="C164" s="3" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>12</v>
-      </c>
-      <c r="B165" t="s">
-        <v>313</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>367</v>
+        <v>8</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -4339,10 +4345,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>360</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>414</v>
+        <v>313</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -4350,9 +4356,20 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
+        <v>360</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>12</v>
+      </c>
+      <c r="B168" t="s">
         <v>424</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C168" t="s">
         <v>52</v>
       </c>
     </row>
@@ -4468,7 +4485,7 @@
     <hyperlink ref="C126" r:id="rId108" xr:uid="{B6255BB1-281E-4413-AA60-7F650B88AE31}"/>
     <hyperlink ref="C127" r:id="rId109" xr:uid="{5C4B4859-6F57-41C9-A767-78BAA0185AC6}"/>
     <hyperlink ref="C164" r:id="rId110" xr:uid="{50F977BC-A580-40CA-99A8-12622C6DC83B}"/>
-    <hyperlink ref="C165" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
+    <hyperlink ref="C166" r:id="rId111" xr:uid="{E1AE9D80-FF8A-4628-B724-F200ECD0FF27}"/>
     <hyperlink ref="C128" r:id="rId112" xr:uid="{812567D3-953B-4D03-AE8C-43607B67208C}"/>
     <hyperlink ref="C129" r:id="rId113" xr:uid="{9F5366E7-2B07-4547-A415-A41154DAF6E8}"/>
     <hyperlink ref="C130" r:id="rId114" xr:uid="{EC814759-6574-4DB1-9594-36303369F2E3}"/>
@@ -4500,7 +4517,7 @@
     <hyperlink ref="C151" r:id="rId140" xr:uid="{2C4DD23A-F9F2-479B-8C24-775407314589}"/>
     <hyperlink ref="C155" r:id="rId141" xr:uid="{A75441B6-9439-4B62-8CA0-49107F5ED25F}"/>
     <hyperlink ref="C156" r:id="rId142" xr:uid="{D1721C97-BCA6-44F5-AE02-814D7DCC88FB}"/>
-    <hyperlink ref="C166" r:id="rId143" xr:uid="{E0507AEA-A22E-45A8-AE1A-2EEE3DA0A0C9}"/>
+    <hyperlink ref="C167" r:id="rId143" xr:uid="{E0507AEA-A22E-45A8-AE1A-2EEE3DA0A0C9}"/>
     <hyperlink ref="C157" r:id="rId144" xr:uid="{10462578-5E0B-41B2-8B9E-998C479B87AC}"/>
     <hyperlink ref="C161" r:id="rId145" xr:uid="{71170706-AE5E-4242-AB9A-7D79E1339A5E}"/>
     <hyperlink ref="C158" r:id="rId146" xr:uid="{DCBD3C2C-5441-4A9F-92FD-4B9D3CCF6F46}"/>
@@ -4511,8 +4528,18 @@
     <hyperlink ref="C113" r:id="rId151" xr:uid="{582F451E-1600-47ED-BE40-CE7AE76AB856}"/>
     <hyperlink ref="C114" r:id="rId152" xr:uid="{45A1DCE2-895B-4281-8D16-DB41A58F6E4F}"/>
     <hyperlink ref="C115" r:id="rId153" xr:uid="{02881D8B-9944-4A49-AB95-663A32B8C1A2}"/>
+    <hyperlink ref="C2" r:id="rId154" xr:uid="{85DAF1CC-5628-4C60-B346-4908A652F97C}"/>
+    <hyperlink ref="C3" r:id="rId155" xr:uid="{5A872234-89C0-492A-8460-9EA083421DC3}"/>
+    <hyperlink ref="C4" r:id="rId156" xr:uid="{5AF9F917-1485-4C96-947D-5C487EB50A65}"/>
+    <hyperlink ref="C8" r:id="rId157" xr:uid="{BD6E03F0-DBA0-466B-9632-F89252F2AA04}"/>
+    <hyperlink ref="C13" r:id="rId158" xr:uid="{5941F684-B34A-4E94-ACEF-1B03290B2246}"/>
+    <hyperlink ref="C15" r:id="rId159" xr:uid="{43FE70A0-4509-4FA4-8327-CCA63DE6D42F}"/>
+    <hyperlink ref="C17" r:id="rId160" xr:uid="{E673FB44-DB5E-4E7F-B0E0-26FE899E7584}"/>
+    <hyperlink ref="C33" r:id="rId161" xr:uid="{1EB03F4F-722C-4A9F-95FD-EBB533917DD6}"/>
+    <hyperlink ref="C38" r:id="rId162" xr:uid="{2F7BB033-B6EF-4DC9-AB5B-70A66A219714}"/>
+    <hyperlink ref="C165" r:id="rId163" xr:uid="{7A3E6189-6A44-4B84-B6D1-ED2EA03581BD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId154"/>
+  <pageSetup orientation="portrait" r:id="rId164"/>
 </worksheet>
 </file>